--- a/Results/single_algorithm/ANF/ANF_TCGA_RNAseq-CNV-Methylation-miRNA-SNPs_eval_on_transNEO_clusterings.xlsx
+++ b/Results/single_algorithm/ANF/ANF_TCGA_RNAseq-CNV-Methylation-miRNA-SNPs_eval_on_transNEO_clusterings.xlsx
@@ -2456,7 +2456,7 @@
         <v>31</v>
       </c>
       <c r="B29" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -4360,7 +4360,7 @@
         <v>269</v>
       </c>
       <c r="B267" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="268">
@@ -5432,7 +5432,7 @@
         <v>403</v>
       </c>
       <c r="B401" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="402">
@@ -5880,7 +5880,7 @@
         <v>459</v>
       </c>
       <c r="B457" t="s">
-        <v>3</v>
+        <v>16</v>
       </c>
     </row>
     <row r="458">
@@ -6904,7 +6904,7 @@
         <v>587</v>
       </c>
       <c r="B585" t="s">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="586">
